--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IndexY\Desktop\paralle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711443F9-9CC2-41F4-BAEB-B78D60EDD877}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2E9BF6-EFC2-4935-999B-5B0268AB5962}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="16">
   <si>
     <t>程序使用的参数</t>
   </si>
@@ -481,7 +481,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.44140625" style="7" bestFit="1" customWidth="1"/>
@@ -524,7 +524,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="5">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -554,7 +554,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="5">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -871,7 +871,10 @@
         <v>720</v>
       </c>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B17" s="5">
+        <v>1020</v>
+      </c>
       <c r="E17" s="9" t="s">
         <v>6</v>
       </c>
@@ -879,7 +882,10 @@
         <v>550</v>
       </c>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B18" s="5">
+        <v>730</v>
+      </c>
       <c r="E18" s="9" t="s">
         <v>7</v>
       </c>
@@ -887,15 +893,21 @@
         <v>500</v>
       </c>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B19" s="5">
+        <v>550</v>
+      </c>
       <c r="E19" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F19" s="10">
-        <v>-45</v>
-      </c>
-    </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B20" s="5">
+        <v>500</v>
+      </c>
       <c r="E20" s="9" t="s">
         <v>9</v>
       </c>
@@ -903,7 +915,10 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B21" s="5">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="s">
         <v>10</v>
       </c>
@@ -911,7 +926,10 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B22" s="5">
+        <v>100</v>
+      </c>
       <c r="E22" s="9" t="s">
         <v>11</v>
       </c>
@@ -919,7 +937,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B23" s="5">
+        <v>80</v>
+      </c>
       <c r="E23" s="9" t="s">
         <v>12</v>
       </c>
@@ -927,7 +948,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B24" s="5">
+        <v>10</v>
+      </c>
       <c r="E24" s="9" t="s">
         <v>13</v>
       </c>
@@ -935,17 +959,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B25" s="5">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B26" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B27" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IndexY\Desktop\paralle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2E9BF6-EFC2-4935-999B-5B0268AB5962}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821E19C5-BDF0-4AEE-9B63-B710AE01964A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="17">
   <si>
     <t>程序使用的参数</t>
   </si>
@@ -68,6 +68,10 @@
   </si>
   <si>
     <t>当前参数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>l_tool</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -75,7 +79,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,8 +100,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -112,6 +122,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -150,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -174,6 +190,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -614,7 +634,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="5">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -847,6 +867,14 @@
       </c>
       <c r="L12" s="6">
         <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="12">
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IndexY\Desktop\paralle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821E19C5-BDF0-4AEE-9B63-B710AE01964A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5AA1F78-D6B0-4135-BBF1-879066556082}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -574,7 +574,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="5">
-        <v>730</v>
+        <v>700</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -634,9 +634,11 @@
         <v>7</v>
       </c>
       <c r="B5" s="5">
+        <v>500</v>
+      </c>
+      <c r="C5" s="3">
         <v>550</v>
       </c>
-      <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
         <v>7</v>
@@ -696,7 +698,9 @@
       <c r="B7" s="5">
         <v>100</v>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="5">
+        <v>120</v>
+      </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3" t="s">
         <v>9</v>
@@ -726,7 +730,9 @@
       <c r="B8" s="5">
         <v>80</v>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="5">
+        <v>90</v>
+      </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
         <v>10</v>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IndexY\Desktop\paralle\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IndexY\Desktop\paralle_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5AA1F78-D6B0-4135-BBF1-879066556082}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C698E57-113E-4B45-BCED-7214D8F04E93}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -166,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -196,6 +196,7 @@
     <xf numFmtId="3" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -543,10 +544,12 @@
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="13">
         <v>1020</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="3">
+        <v>1020</v>
+      </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
         <v>4</v>
@@ -573,10 +576,12 @@
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="13">
+        <v>720</v>
+      </c>
+      <c r="C3" s="3">
         <v>700</v>
       </c>
-      <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
         <v>5</v>
@@ -603,10 +608,12 @@
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="13">
         <v>550</v>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3">
+        <v>550</v>
+      </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
         <v>6</v>
@@ -633,8 +640,8 @@
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="5">
-        <v>500</v>
+      <c r="B5" s="13">
+        <v>550</v>
       </c>
       <c r="C5" s="3">
         <v>550</v>
@@ -696,7 +703,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="5">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C7" s="5">
         <v>120</v>
@@ -728,7 +735,7 @@
         <v>10</v>
       </c>
       <c r="B8" s="5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C8" s="5">
         <v>90</v>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IndexY\Desktop\paralle_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C698E57-113E-4B45-BCED-7214D8F04E93}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC3083F-A0C4-4BC8-9378-9C4B181ACBB4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="32">
   <si>
     <t>程序使用的参数</t>
   </si>
@@ -73,6 +73,61 @@
   <si>
     <t>l_tool</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>b_dir1(deg)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>b_dir2(deg)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>b_dir3(deg)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>b_dir4(deg)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>b_dir5(deg)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>m_dir1(deg)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>m_dir2(deg)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>m_dir3(deg)</t>
+  </si>
+  <si>
+    <t>m_dir4(deg)</t>
+  </si>
+  <si>
+    <t>m_dir5(deg)</t>
+  </si>
+  <si>
+    <t>L0_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>L0_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>L0_3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>L0_4</t>
+  </si>
+  <si>
+    <t>L0_5</t>
   </si>
 </sst>
 </file>
@@ -166,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -197,6 +252,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -502,7 +560,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.44140625" style="7" bestFit="1" customWidth="1"/>
@@ -857,7 +915,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -887,34 +945,64 @@
         <v>16</v>
       </c>
       <c r="B13" s="12">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="5">
+        <v>90</v>
+      </c>
       <c r="E14" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H14" s="5">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="5">
+        <v>210</v>
+      </c>
       <c r="E15" s="9" t="s">
         <v>4</v>
       </c>
       <c r="F15" s="10">
         <v>1030</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H15" s="5">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="5">
+        <v>-30</v>
+      </c>
       <c r="E16" s="9" t="s">
         <v>5</v>
       </c>
       <c r="F16" s="10">
         <v>720</v>
       </c>
-    </row>
-    <row r="17" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="H16" s="5">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
+        <v>20</v>
+      </c>
       <c r="B17" s="5">
-        <v>1020</v>
+        <v>30</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>6</v>
@@ -922,10 +1010,16 @@
       <c r="F17" s="10">
         <v>550</v>
       </c>
-    </row>
-    <row r="18" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="H17" s="5">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A18" s="14" t="s">
+        <v>21</v>
+      </c>
       <c r="B18" s="5">
-        <v>730</v>
+        <v>150</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>7</v>
@@ -933,10 +1027,16 @@
       <c r="F18" s="10">
         <v>500</v>
       </c>
-    </row>
-    <row r="19" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="H18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
+        <v>22</v>
+      </c>
       <c r="B19" s="5">
-        <v>550</v>
+        <v>90</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>8</v>
@@ -944,10 +1044,16 @@
       <c r="F19" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="H19" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
+        <v>23</v>
+      </c>
       <c r="B20" s="5">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>9</v>
@@ -955,10 +1061,16 @@
       <c r="F20" s="10">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="H20" s="5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>24</v>
+      </c>
       <c r="B21" s="5">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>10</v>
@@ -966,10 +1078,16 @@
       <c r="F21" s="10">
         <v>80</v>
       </c>
-    </row>
-    <row r="22" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="H21" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
+        <v>25</v>
+      </c>
       <c r="B22" s="5">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>11</v>
@@ -977,10 +1095,16 @@
       <c r="F22" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="H22" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
+        <v>26</v>
+      </c>
       <c r="B23" s="5">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>12</v>
@@ -988,10 +1112,16 @@
       <c r="F23" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="H23" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A24" s="14" t="s">
+        <v>27</v>
+      </c>
       <c r="B24" s="5">
-        <v>10</v>
+        <v>600</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>13</v>
@@ -999,10 +1129,16 @@
       <c r="F24" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="H24" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="B25" s="5">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>14</v>
@@ -1011,14 +1147,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>29</v>
+      </c>
       <c r="B26" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
+        <v>30</v>
+      </c>
       <c r="B27" s="5">
-        <v>0</v>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A28" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="5">
+        <v>600</v>
       </c>
     </row>
   </sheetData>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20338"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IndexY\Desktop\paralle_\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\segeiY\Desktop\paralle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C698E57-113E-4B45-BCED-7214D8F04E93}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA84246-1164-4880-B9D2-5B844AB67194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5544" yWindow="5688" windowWidth="19920" windowHeight="9948" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="19">
   <si>
     <t>程序使用的参数</t>
   </si>
@@ -72,6 +72,14 @@
   </si>
   <si>
     <t>l_tool</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>my para</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>from diroam</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -166,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -174,7 +182,6 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -184,19 +191,15 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -505,70 +508,65 @@
   <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="10">
+        <v>5000</v>
+      </c>
+      <c r="C2">
         <v>1020</v>
       </c>
-      <c r="C2" s="3">
-        <v>1020</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <v>1030</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="5">
         <v>740</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3" t="s">
+      <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="5">
         <v>740</v>
       </c>
     </row>
@@ -576,31 +574,28 @@
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="10">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>700</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="5">
         <v>720</v>
       </c>
-      <c r="C3" s="3">
-        <v>700</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="s">
+      <c r="H3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="6">
-        <v>720</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="5">
+        <v>570</v>
+      </c>
+      <c r="K3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="6">
-        <v>570</v>
-      </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>570</v>
       </c>
     </row>
@@ -608,31 +603,28 @@
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="10">
+        <v>1281</v>
+      </c>
+      <c r="C4">
         <v>550</v>
       </c>
-      <c r="C4" s="3">
-        <v>550</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3" t="s">
+      <c r="E4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>700</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3" t="s">
+      <c r="H4" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>500</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3" t="s">
+      <c r="K4" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="5">
         <v>350</v>
       </c>
     </row>
@@ -640,31 +632,28 @@
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="10">
+        <v>1076</v>
+      </c>
+      <c r="C5">
         <v>550</v>
       </c>
-      <c r="C5" s="3">
-        <v>550</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3" t="s">
+      <c r="E5" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>600</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
+      <c r="H5" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>450</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3" t="s">
+      <c r="K5" t="s">
         <v>7</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="5">
         <v>300</v>
       </c>
     </row>
@@ -672,29 +661,25 @@
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="5">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3" t="s">
+      <c r="B6" s="4">
+        <v>250</v>
+      </c>
+      <c r="E6" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>-60</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3" t="s">
+      <c r="H6" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <v>-45</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3" t="s">
+      <c r="K6" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>-30</v>
       </c>
     </row>
@@ -702,31 +687,28 @@
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
+        <v>180</v>
+      </c>
+      <c r="C7" s="4">
         <v>120</v>
       </c>
-      <c r="C7" s="5">
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="5">
         <v>120</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3" t="s">
+      <c r="H7" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="6">
-        <v>120</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="5">
+        <v>80</v>
+      </c>
+      <c r="K7" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="6">
-        <v>80</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <v>60</v>
       </c>
     </row>
@@ -734,31 +716,28 @@
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
+        <v>180</v>
+      </c>
+      <c r="C8" s="4">
         <v>90</v>
       </c>
-      <c r="C8" s="5">
-        <v>90</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3" t="s">
+      <c r="E8" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <v>100</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3" t="s">
+      <c r="H8" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <v>70</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3" t="s">
+      <c r="K8" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="5">
         <v>50</v>
       </c>
     </row>
@@ -766,29 +745,25 @@
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
+        <v>340</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="5">
+        <v>20</v>
+      </c>
+      <c r="H9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="5">
         <v>10</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3" t="s">
+      <c r="K9" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="6">
-        <v>20</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="6">
-        <v>10</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L9" s="6">
+      <c r="L9" s="5">
         <v>10</v>
       </c>
     </row>
@@ -796,29 +771,25 @@
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="5">
-        <v>0</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3" t="s">
+      <c r="B10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="6">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3" t="s">
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="6">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3" t="s">
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
         <v>12</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <v>0</v>
       </c>
     </row>
@@ -826,29 +797,25 @@
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="5">
-        <v>0</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3" t="s">
+      <c r="B11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3" t="s">
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="6">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3" t="s">
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
         <v>13</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="5">
         <v>0</v>
       </c>
     </row>
@@ -856,168 +823,164 @@
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="5">
-        <v>0</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3" t="s">
+      <c r="B12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="6">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3" t="s">
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="6">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3" t="s">
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
         <v>14</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="9">
         <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="10"/>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="7">
         <v>1030</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="7">
         <v>720</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>1020</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="7">
         <v>550</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>730</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="7">
         <v>500</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>550</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>500</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="7">
         <v>100</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="B21" s="5">
-        <v>0</v>
-      </c>
-      <c r="E21" s="9" t="s">
+      <c r="B21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="7">
         <v>80</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="B22" s="5">
+      <c r="B22" s="4">
         <v>100</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="7">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="B23" s="5">
+      <c r="B23" s="4">
         <v>80</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="B24" s="5">
+      <c r="B24" s="4">
         <v>10</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="B25" s="5">
-        <v>0</v>
-      </c>
-      <c r="E25" s="9" t="s">
+      <c r="B25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="B26" s="5">
+      <c r="B26" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="B27" s="5">
+      <c r="B27" s="4">
         <v>0</v>
       </c>
     </row>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IndexY\Desktop\paralle_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE42797F-E1A4-4DB9-AA00-4D25192EE83C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99183E2-E391-42B3-9486-A17E2800E409}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="39">
   <si>
     <t>初始参数</t>
   </si>
@@ -131,10 +131,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>structure_err</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>一种轻量化五轴全并联加工机器人研发与应用</t>
   </si>
   <si>
@@ -147,6 +143,18 @@
   </si>
   <si>
     <t>一种五轴并联加工单元的参数与刚度优化设计</t>
+  </si>
+  <si>
+    <t>current</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>modify_base_current</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>need to design</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -590,7 +598,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.44140625" style="5" bestFit="1" customWidth="1"/>
@@ -609,22 +617,26 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" s="11"/>
+      <c r="G1" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="H1" s="11"/>
       <c r="I1" s="1" t="s">
         <v>0</v>
@@ -660,7 +672,9 @@
       <c r="F2" s="17">
         <v>2000</v>
       </c>
-      <c r="G2" s="17"/>
+      <c r="G2" s="11">
+        <v>1020</v>
+      </c>
       <c r="H2" s="17"/>
       <c r="I2" s="1" t="s">
         <v>3</v>
@@ -691,7 +705,7 @@
         <v>720</v>
       </c>
       <c r="C3" s="11">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="D3" s="11">
         <v>720</v>
@@ -702,7 +716,9 @@
       <c r="F3" s="17">
         <v>0</v>
       </c>
-      <c r="G3" s="17"/>
+      <c r="G3" s="11">
+        <v>720</v>
+      </c>
       <c r="H3" s="17"/>
       <c r="I3" s="1" t="s">
         <v>4</v>
@@ -744,7 +760,9 @@
       <c r="F4" s="17">
         <v>650</v>
       </c>
-      <c r="G4" s="11"/>
+      <c r="G4" s="11">
+        <v>550</v>
+      </c>
       <c r="H4" s="11"/>
       <c r="I4" s="1" t="s">
         <v>5</v>
@@ -772,10 +790,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="11">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="C5" s="11">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="D5" s="11">
         <v>500</v>
@@ -786,7 +804,9 @@
       <c r="F5" s="17">
         <v>650</v>
       </c>
-      <c r="G5" s="11"/>
+      <c r="G5" s="11">
+        <v>550</v>
+      </c>
       <c r="H5" s="11"/>
       <c r="I5" s="1" t="s">
         <v>6</v>
@@ -816,7 +836,9 @@
       <c r="B6" s="12">
         <v>0</v>
       </c>
-      <c r="C6" s="11"/>
+      <c r="C6" s="12">
+        <v>0</v>
+      </c>
       <c r="D6" s="12">
         <v>0</v>
       </c>
@@ -826,7 +848,9 @@
       <c r="F6" s="13">
         <v>0</v>
       </c>
-      <c r="G6" s="13"/>
+      <c r="G6" s="12">
+        <v>0</v>
+      </c>
       <c r="H6" s="13"/>
       <c r="I6" s="1" t="s">
         <v>7</v>
@@ -854,10 +878,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="12">
+        <v>100</v>
+      </c>
+      <c r="C7" s="12">
         <v>150</v>
-      </c>
-      <c r="C7" s="12">
-        <v>120</v>
       </c>
       <c r="D7" s="12">
         <v>100</v>
@@ -868,7 +892,9 @@
       <c r="F7" s="13">
         <v>180</v>
       </c>
-      <c r="G7" s="13"/>
+      <c r="G7" s="12">
+        <v>150</v>
+      </c>
       <c r="H7" s="13"/>
       <c r="I7" s="1" t="s">
         <v>8</v>
@@ -896,10 +922,10 @@
         <v>9</v>
       </c>
       <c r="B8" s="12">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C8" s="12">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D8" s="12">
         <v>80</v>
@@ -910,7 +936,9 @@
       <c r="F8" s="13">
         <v>90</v>
       </c>
-      <c r="G8" s="13"/>
+      <c r="G8" s="12">
+        <v>75</v>
+      </c>
       <c r="H8" s="13"/>
       <c r="I8" s="1" t="s">
         <v>9</v>
@@ -938,9 +966,11 @@
         <v>10</v>
       </c>
       <c r="B9" s="12">
+        <v>10</v>
+      </c>
+      <c r="C9" s="12">
         <v>315</v>
       </c>
-      <c r="C9" s="11"/>
       <c r="D9" s="12">
         <v>10</v>
       </c>
@@ -950,7 +980,9 @@
       <c r="F9" s="13">
         <v>370</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" s="12">
+        <v>315</v>
+      </c>
       <c r="H9" s="13"/>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -973,475 +1005,481 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="12">
-        <v>0</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="12">
-        <v>0</v>
-      </c>
-      <c r="E10" s="13">
-        <v>0</v>
-      </c>
-      <c r="F10" s="13">
-        <v>0</v>
-      </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="4">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M10" s="4">
-        <v>0</v>
-      </c>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="12">
-        <v>0</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="12">
-        <v>0</v>
-      </c>
-      <c r="E11" s="13">
-        <v>0</v>
-      </c>
-      <c r="F11" s="13">
-        <v>0</v>
-      </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J11" s="4">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M11" s="4">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P11" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
-        <v>13</v>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="15">
+        <v>150</v>
+      </c>
+      <c r="C10" s="15">
+        <v>150</v>
+      </c>
+      <c r="D10" s="15">
+        <v>150</v>
+      </c>
+      <c r="E10" s="15">
+        <v>0</v>
+      </c>
+      <c r="F10" s="15">
+        <v>220</v>
+      </c>
+      <c r="G10" s="15">
+        <v>140</v>
+      </c>
+      <c r="H10" s="15"/>
+    </row>
+    <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="15">
+        <v>155</v>
+      </c>
+      <c r="C11" s="15">
+        <v>155</v>
+      </c>
+      <c r="D11" s="15">
+        <v>155</v>
+      </c>
+      <c r="E11" s="15">
+        <v>155</v>
+      </c>
+      <c r="F11" s="15">
+        <v>155</v>
+      </c>
+      <c r="G11" s="15">
+        <v>155</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="L11" s="3">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
+        <v>16</v>
       </c>
       <c r="B12" s="12">
-        <v>0</v>
-      </c>
-      <c r="C12" s="11"/>
+        <v>90</v>
+      </c>
+      <c r="C12" s="12">
+        <v>90</v>
+      </c>
       <c r="D12" s="12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E12" s="13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F12" s="13">
-        <v>0</v>
-      </c>
-      <c r="G12" s="13"/>
+        <v>90</v>
+      </c>
+      <c r="G12" s="12">
+        <v>90</v>
+      </c>
       <c r="H12" s="13"/>
-      <c r="I12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="4">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M12" s="4">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P12" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="15">
-        <v>190</v>
-      </c>
-      <c r="C13" s="11">
-        <v>150</v>
-      </c>
-      <c r="D13" s="15">
-        <v>150</v>
-      </c>
-      <c r="E13" s="15">
-        <v>0</v>
-      </c>
-      <c r="F13" s="15">
-        <v>220</v>
-      </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="I12" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="8">
+        <v>1030</v>
+      </c>
+      <c r="L12" s="3">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="12">
+        <v>210</v>
+      </c>
+      <c r="C13" s="12">
+        <v>210</v>
+      </c>
+      <c r="D13" s="12">
+        <v>210</v>
+      </c>
+      <c r="E13" s="13">
+        <v>210</v>
+      </c>
+      <c r="F13" s="13">
+        <v>210</v>
+      </c>
+      <c r="G13" s="12">
+        <v>210</v>
+      </c>
+      <c r="H13" s="13"/>
+      <c r="I13" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J13" s="8">
+        <v>720</v>
+      </c>
+      <c r="L13" s="3">
+        <v>550</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="15">
-        <v>155</v>
-      </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="15">
-        <v>155</v>
-      </c>
-      <c r="E14" s="15">
-        <v>155</v>
-      </c>
-      <c r="F14" s="15">
-        <v>155</v>
-      </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="A14" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="12">
+        <v>-30</v>
+      </c>
+      <c r="C14" s="12">
+        <v>-30</v>
+      </c>
+      <c r="D14" s="12">
+        <v>-30</v>
+      </c>
+      <c r="E14" s="13">
+        <v>-30</v>
+      </c>
+      <c r="F14" s="13">
+        <v>-30</v>
+      </c>
+      <c r="G14" s="12">
+        <v>-30</v>
+      </c>
+      <c r="H14" s="13"/>
       <c r="I14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J14" s="8"/>
+        <v>5</v>
+      </c>
+      <c r="J14" s="8">
+        <v>550</v>
+      </c>
       <c r="L14" s="3">
-        <v>1020</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B15" s="12">
-        <v>90</v>
-      </c>
-      <c r="C15" s="11"/>
+        <v>30</v>
+      </c>
+      <c r="C15" s="12">
+        <v>30</v>
+      </c>
       <c r="D15" s="12">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="E15" s="13">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F15" s="13">
-        <v>90</v>
-      </c>
-      <c r="G15" s="13"/>
+        <f>90-33.3</f>
+        <v>56.7</v>
+      </c>
+      <c r="G15" s="12">
+        <v>45</v>
+      </c>
       <c r="H15" s="13"/>
       <c r="I15" s="7" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J15" s="8">
-        <v>1030</v>
+        <v>500</v>
       </c>
       <c r="L15" s="3">
-        <v>730</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B16" s="12">
-        <v>210</v>
-      </c>
-      <c r="C16" s="11"/>
+        <v>150</v>
+      </c>
+      <c r="C16" s="12">
+        <v>150</v>
+      </c>
       <c r="D16" s="12">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="E16" s="13">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="F16" s="13">
-        <v>210</v>
-      </c>
-      <c r="G16" s="13"/>
+        <f>90+33.3</f>
+        <v>123.3</v>
+      </c>
+      <c r="G16" s="12">
+        <v>135</v>
+      </c>
       <c r="H16" s="13"/>
       <c r="I16" s="7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J16" s="8">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="L16" s="3">
-        <v>550</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B17" s="12">
-        <v>-30</v>
-      </c>
-      <c r="C17" s="11"/>
+        <v>90</v>
+      </c>
+      <c r="C17" s="12">
+        <v>90</v>
+      </c>
       <c r="D17" s="12">
-        <v>-30</v>
+        <v>90</v>
       </c>
       <c r="E17" s="13">
-        <v>-30</v>
+        <v>90</v>
       </c>
       <c r="F17" s="13">
-        <v>-30</v>
-      </c>
-      <c r="G17" s="13"/>
+        <v>90</v>
+      </c>
+      <c r="G17" s="12">
+        <v>90</v>
+      </c>
       <c r="H17" s="13"/>
       <c r="I17" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J17" s="8">
-        <v>550</v>
+        <v>100</v>
       </c>
       <c r="L17" s="3">
-        <v>500</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B18" s="12">
-        <v>57</v>
-      </c>
-      <c r="C18" s="11"/>
+        <v>210</v>
+      </c>
+      <c r="C18" s="12">
+        <v>210</v>
+      </c>
       <c r="D18" s="12">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="E18" s="13">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="F18" s="13">
-        <f>90-33.3</f>
-        <v>56.7</v>
-      </c>
-      <c r="G18" s="13"/>
+        <v>210</v>
+      </c>
+      <c r="G18" s="12">
+        <v>210</v>
+      </c>
       <c r="H18" s="13"/>
       <c r="I18" s="7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J18" s="8">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="L18" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B19" s="12">
-        <v>123</v>
-      </c>
-      <c r="C19" s="11"/>
+        <v>-30</v>
+      </c>
+      <c r="C19" s="12">
+        <v>-30</v>
+      </c>
       <c r="D19" s="12">
-        <v>150</v>
+        <v>-30</v>
       </c>
       <c r="E19" s="13">
-        <v>130</v>
+        <v>-30</v>
       </c>
       <c r="F19" s="13">
-        <f>90+33.3</f>
-        <v>123.3</v>
-      </c>
-      <c r="G19" s="13"/>
+        <v>-30</v>
+      </c>
+      <c r="G19" s="12">
+        <v>-30</v>
+      </c>
       <c r="H19" s="13"/>
       <c r="I19" s="7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J19" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L19" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B20" s="12">
-        <v>90</v>
-      </c>
-      <c r="C20" s="11"/>
+        <v>30</v>
+      </c>
+      <c r="C20" s="12">
+        <v>40</v>
+      </c>
       <c r="D20" s="12">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="E20" s="13">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="F20" s="13">
-        <v>90</v>
-      </c>
-      <c r="G20" s="13"/>
+        <v>40</v>
+      </c>
+      <c r="G20" s="12">
+        <v>45</v>
+      </c>
       <c r="H20" s="13"/>
       <c r="I20" s="7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J20" s="8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B21" s="12">
-        <v>210</v>
-      </c>
-      <c r="C21" s="11"/>
+        <v>150</v>
+      </c>
+      <c r="C21" s="12">
+        <v>140</v>
+      </c>
       <c r="D21" s="12">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="E21" s="13">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="F21" s="13">
-        <v>210</v>
-      </c>
-      <c r="G21" s="13"/>
+        <v>140</v>
+      </c>
+      <c r="G21" s="12">
+        <v>135</v>
+      </c>
       <c r="H21" s="13"/>
       <c r="I21" s="7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J21" s="8">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B22" s="12">
-        <v>-30</v>
-      </c>
-      <c r="C22" s="11"/>
+        <v>600</v>
+      </c>
+      <c r="C22" s="12">
+        <v>600</v>
+      </c>
       <c r="D22" s="12">
-        <v>-30</v>
+        <v>600</v>
       </c>
       <c r="E22" s="13">
-        <v>-30</v>
+        <v>600</v>
       </c>
       <c r="F22" s="13">
-        <v>-30</v>
-      </c>
-      <c r="G22" s="13"/>
+        <v>600</v>
+      </c>
+      <c r="G22" s="12">
+        <v>600</v>
+      </c>
       <c r="H22" s="13"/>
       <c r="I22" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J22" s="8">
-        <v>10</v>
-      </c>
-      <c r="L22" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B23" s="12">
-        <v>40</v>
-      </c>
-      <c r="C23" s="11"/>
+        <v>600</v>
+      </c>
+      <c r="C23" s="12">
+        <v>600</v>
+      </c>
       <c r="D23" s="12">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="E23" s="13">
-        <v>45</v>
+        <v>600</v>
       </c>
       <c r="F23" s="13">
-        <v>40</v>
-      </c>
-      <c r="G23" s="13"/>
+        <v>600</v>
+      </c>
+      <c r="G23" s="12">
+        <v>600</v>
+      </c>
       <c r="H23" s="13"/>
-      <c r="I23" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="J23" s="8">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
     </row>
     <row r="24" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B24" s="12">
-        <v>140</v>
-      </c>
-      <c r="C24" s="11"/>
+        <v>600</v>
+      </c>
+      <c r="C24" s="12">
+        <v>600</v>
+      </c>
       <c r="D24" s="12">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="E24" s="13">
-        <v>135</v>
+        <v>600</v>
       </c>
       <c r="F24" s="13">
-        <v>140</v>
-      </c>
-      <c r="G24" s="13"/>
+        <v>600</v>
+      </c>
+      <c r="G24" s="12">
+        <v>600</v>
+      </c>
       <c r="H24" s="13"/>
-      <c r="I24" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J24" s="8">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
     </row>
     <row r="25" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B25" s="12">
         <v>600</v>
       </c>
-      <c r="C25" s="11"/>
+      <c r="C25" s="12">
+        <v>600</v>
+      </c>
       <c r="D25" s="12">
         <v>600</v>
       </c>
@@ -1451,23 +1489,21 @@
       <c r="F25" s="13">
         <v>600</v>
       </c>
-      <c r="G25" s="13"/>
+      <c r="G25" s="12">
+        <v>600</v>
+      </c>
       <c r="H25" s="13"/>
-      <c r="I25" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J25" s="8">
-        <v>0</v>
-      </c>
     </row>
     <row r="26" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B26" s="12">
         <v>600</v>
       </c>
-      <c r="C26" s="11"/>
+      <c r="C26" s="12">
+        <v>600</v>
+      </c>
       <c r="D26" s="12">
         <v>600</v>
       </c>
@@ -1477,68 +1513,10 @@
       <c r="F26" s="13">
         <v>600</v>
       </c>
-      <c r="G26" s="13"/>
+      <c r="G26" s="12">
+        <v>600</v>
+      </c>
       <c r="H26" s="13"/>
-    </row>
-    <row r="27" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A27" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="12">
-        <v>600</v>
-      </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="12">
-        <v>600</v>
-      </c>
-      <c r="E27" s="13">
-        <v>600</v>
-      </c>
-      <c r="F27" s="13">
-        <v>600</v>
-      </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-    </row>
-    <row r="28" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A28" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="12">
-        <v>600</v>
-      </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="12">
-        <v>600</v>
-      </c>
-      <c r="E28" s="13">
-        <v>600</v>
-      </c>
-      <c r="F28" s="13">
-        <v>600</v>
-      </c>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-    </row>
-    <row r="29" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A29" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="12">
-        <v>600</v>
-      </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="12">
-        <v>600</v>
-      </c>
-      <c r="E29" s="13">
-        <v>600</v>
-      </c>
-      <c r="F29" s="13">
-        <v>600</v>
-      </c>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IndexY\Desktop\paralle_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99183E2-E391-42B3-9486-A17E2800E409}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF9AB5C-0AB0-4A11-BC56-6A7755B69025}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -966,7 +966,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="12">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C9" s="12">
         <v>315</v>
@@ -1331,7 +1331,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="12">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C20" s="12">
         <v>40</v>
@@ -1364,7 +1364,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="12">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C21" s="12">
         <v>140</v>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IndexY\Desktop\paralle_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF9AB5C-0AB0-4A11-BC56-6A7755B69025}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7DBB0E-6378-46C0-9CE2-C60D6C3FD5C2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="41">
   <si>
     <t>初始参数</t>
   </si>
@@ -154,6 +154,14 @@
   </si>
   <si>
     <t>need to design</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>v1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>v2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -161,6 +169,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -276,9 +287,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -292,6 +300,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -598,25 +609,25 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.44140625" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="13.5546875" style="5" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="11" width="13.5546875" style="5" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" style="5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -634,60 +645,65 @@
       <c r="F1" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="11"/>
-      <c r="I1" s="1" t="s">
+      <c r="H1" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="J1" s="2"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
-        <v>1</v>
       </c>
       <c r="M1" s="2"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="18">
         <v>1020</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="18">
         <v>1020</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="18">
         <v>1020</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="18">
         <v>2000</v>
       </c>
-      <c r="F2" s="17">
+      <c r="F2" s="18">
         <v>2000</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="18">
         <v>1020</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="4">
-        <v>1030</v>
-      </c>
-      <c r="K2" s="1"/>
+      <c r="H2" s="18">
+        <v>1020</v>
+      </c>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
       <c r="L2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="M2" s="4">
-        <v>740</v>
+        <v>1030</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1" t="s">
@@ -696,42 +712,47 @@
       <c r="P2" s="4">
         <v>740</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S2" s="4">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="18">
         <v>720</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="18">
         <v>720</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="18">
         <v>720</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="18">
         <v>0</v>
       </c>
-      <c r="F3" s="17">
+      <c r="F3" s="18">
         <v>0</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="18">
         <v>720</v>
       </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J3" s="4">
+      <c r="H3" s="18">
         <v>720</v>
       </c>
-      <c r="K3" s="1"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
       <c r="L3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="M3" s="4">
-        <v>570</v>
+        <v>720</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1" t="s">
@@ -740,262 +761,292 @@
       <c r="P3" s="4">
         <v>570</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S3" s="4">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="18">
         <v>550</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="18">
         <v>550</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="18">
         <v>550</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="18">
         <v>1281</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="18">
         <v>650</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="18">
         <v>550</v>
       </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4" s="4">
-        <v>700</v>
-      </c>
-      <c r="K4" s="1"/>
+      <c r="H4" s="18">
+        <v>550</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
       <c r="L4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="M4" s="4">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="P4" s="4">
+        <v>500</v>
+      </c>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="S4" s="4">
         <v>350</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="18">
         <v>500</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="18">
         <v>500</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="18">
         <v>500</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="18">
         <v>1076</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="18">
         <v>650</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="18">
         <v>550</v>
       </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" s="4">
-        <v>600</v>
-      </c>
-      <c r="K5" s="1"/>
+      <c r="H5" s="18">
+        <v>500</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
       <c r="L5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="M5" s="4">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="P5" s="4">
+        <v>450</v>
+      </c>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="S5" s="4">
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="18">
+        <v>-2.57</v>
+      </c>
+      <c r="C6" s="18">
         <v>0</v>
       </c>
-      <c r="C6" s="12">
+      <c r="D6" s="18">
         <v>0</v>
       </c>
-      <c r="D6" s="12">
+      <c r="E6" s="18">
+        <v>250</v>
+      </c>
+      <c r="F6" s="18">
         <v>0</v>
       </c>
-      <c r="E6" s="13">
-        <v>250</v>
-      </c>
-      <c r="F6" s="13">
+      <c r="G6" s="18">
         <v>0</v>
       </c>
-      <c r="G6" s="12">
-        <v>0</v>
-      </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J6" s="4">
-        <v>-60</v>
-      </c>
-      <c r="K6" s="1"/>
+      <c r="H6" s="18">
+        <v>-18</v>
+      </c>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
       <c r="L6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="M6" s="4">
-        <v>-45</v>
+        <v>-60</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="P6" s="4">
+        <v>-45</v>
+      </c>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S6" s="4">
         <v>-30</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="18">
+        <v>148.5</v>
+      </c>
+      <c r="C7" s="18">
+        <v>150</v>
+      </c>
+      <c r="D7" s="18">
         <v>100</v>
       </c>
-      <c r="C7" s="12">
+      <c r="E7" s="18">
+        <v>180</v>
+      </c>
+      <c r="F7" s="18">
+        <v>180</v>
+      </c>
+      <c r="G7" s="18">
         <v>150</v>
       </c>
-      <c r="D7" s="12">
-        <v>100</v>
-      </c>
-      <c r="E7" s="13">
-        <v>180</v>
-      </c>
-      <c r="F7" s="13">
-        <v>180</v>
-      </c>
-      <c r="G7" s="12">
+      <c r="H7" s="18">
         <v>150</v>
       </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J7" s="4">
-        <v>120</v>
-      </c>
-      <c r="K7" s="1"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
       <c r="L7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="M7" s="4">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="P7" s="4">
+        <v>80</v>
+      </c>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="S7" s="4">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="18">
+        <v>62.87</v>
+      </c>
+      <c r="C8" s="18">
         <v>80</v>
       </c>
-      <c r="C8" s="12">
+      <c r="D8" s="18">
         <v>80</v>
       </c>
-      <c r="D8" s="12">
-        <v>80</v>
-      </c>
-      <c r="E8" s="13">
+      <c r="E8" s="18">
         <v>180</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="18">
         <v>90</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="18">
         <v>75</v>
       </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="4">
-        <v>100</v>
-      </c>
-      <c r="K8" s="1"/>
+      <c r="H8" s="18">
+        <v>40</v>
+      </c>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
       <c r="L8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="M8" s="4">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="P8" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="12">
-        <v>30</v>
-      </c>
-      <c r="C9" s="12">
+      <c r="B9" s="18">
+        <v>128</v>
+      </c>
+      <c r="C9" s="18">
         <v>315</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="18">
         <v>10</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="18">
         <v>340</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="18">
         <v>370</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="18">
         <v>315</v>
       </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" s="4">
-        <v>20</v>
-      </c>
-      <c r="K9" s="1"/>
+      <c r="H9" s="18">
+        <v>120</v>
+      </c>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
       <c r="L9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="M9" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1" t="s">
@@ -1004,519 +1055,611 @@
       <c r="P9" s="4">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S9" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="15" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="18">
         <v>150</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="18">
         <v>150</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="18">
         <v>150</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="18">
         <v>0</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="18">
         <v>220</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="18">
         <v>140</v>
       </c>
-      <c r="H10" s="15"/>
-    </row>
-    <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
+      <c r="H10" s="18">
+        <v>150</v>
+      </c>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+    </row>
+    <row r="11" spans="1:19" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="18">
         <v>155</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="18">
         <v>155</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="18">
         <v>155</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="18">
         <v>155</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="18">
         <v>155</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="18">
         <v>155</v>
       </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="7" t="s">
+      <c r="H11" s="18">
+        <v>155</v>
+      </c>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="8"/>
-      <c r="L11" s="3">
+      <c r="M11" s="8"/>
+      <c r="O11" s="3">
         <v>1020</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A12" s="16" t="s">
+    <row r="12" spans="1:19" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="18">
         <v>90</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="18">
         <v>90</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="18">
         <v>90</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="18">
         <v>90</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="18">
         <v>90</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="18">
         <v>90</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="7" t="s">
+      <c r="H12" s="18">
+        <v>90</v>
+      </c>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="J12" s="8">
+      <c r="M12" s="8">
         <v>1030</v>
       </c>
-      <c r="L12" s="3">
+      <c r="O12" s="3">
         <v>730</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A13" s="16" t="s">
+    <row r="13" spans="1:19" ht="15" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="18">
         <v>210</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="18">
         <v>210</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="18">
         <v>210</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="18">
         <v>210</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="18">
         <v>210</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="18">
         <v>210</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="7" t="s">
+      <c r="H13" s="18">
+        <v>210</v>
+      </c>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J13" s="8">
+      <c r="M13" s="8">
         <v>720</v>
       </c>
-      <c r="L13" s="3">
+      <c r="O13" s="3">
         <v>550</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
+    <row r="14" spans="1:19" ht="15" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="18">
         <v>-30</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="18">
         <v>-30</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="18">
         <v>-30</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="18">
         <v>-30</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="18">
         <v>-30</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="18">
         <v>-30</v>
       </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="7" t="s">
+      <c r="H14" s="18">
+        <v>-30</v>
+      </c>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="J14" s="8">
+      <c r="M14" s="8">
         <v>550</v>
       </c>
-      <c r="L14" s="3">
+      <c r="O14" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A15" s="16" t="s">
+    <row r="15" spans="1:19" ht="15" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="18">
         <v>30</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="18">
         <v>30</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="18">
         <v>30</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="18">
         <v>50</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="18">
         <f>90-33.3</f>
         <v>56.7</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="18">
         <v>45</v>
       </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="7" t="s">
+      <c r="H15" s="18">
+        <v>30</v>
+      </c>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J15" s="8">
+      <c r="M15" s="8">
         <v>500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="O15" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
+    <row r="16" spans="1:19" ht="15" x14ac:dyDescent="0.3">
+      <c r="A16" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="18">
         <v>150</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="18">
         <v>150</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="18">
         <v>150</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="18">
         <v>130</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="18">
         <f>90+33.3</f>
         <v>123.3</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="18">
         <v>135</v>
       </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="7" t="s">
+      <c r="H16" s="18">
+        <v>150</v>
+      </c>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J16" s="8">
+      <c r="M16" s="8">
         <v>0</v>
       </c>
-      <c r="L16" s="3">
+      <c r="O16" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A17" s="16" t="s">
+    <row r="17" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="18">
         <v>90</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="18">
         <v>90</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="18">
         <v>90</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="18">
         <v>90</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="18">
         <v>90</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="18">
         <v>90</v>
       </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="7" t="s">
+      <c r="H17" s="18">
+        <v>90</v>
+      </c>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J17" s="8">
+      <c r="M17" s="8">
         <v>100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="O17" s="3">
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="s">
+    <row r="18" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="18">
+        <v>195</v>
+      </c>
+      <c r="C18" s="18">
         <v>210</v>
       </c>
-      <c r="C18" s="12">
+      <c r="D18" s="18">
         <v>210</v>
       </c>
-      <c r="D18" s="12">
+      <c r="E18" s="18">
         <v>210</v>
       </c>
-      <c r="E18" s="13">
+      <c r="F18" s="18">
         <v>210</v>
       </c>
-      <c r="F18" s="13">
+      <c r="G18" s="18">
         <v>210</v>
       </c>
-      <c r="G18" s="12">
+      <c r="H18" s="18">
         <v>210</v>
       </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J18" s="8">
+      <c r="M18" s="8">
         <v>80</v>
       </c>
-      <c r="L18" s="3">
+      <c r="O18" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A19" s="16" t="s">
+    <row r="19" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="18">
+        <v>-15</v>
+      </c>
+      <c r="C19" s="18">
         <v>-30</v>
       </c>
-      <c r="C19" s="12">
+      <c r="D19" s="18">
         <v>-30</v>
       </c>
-      <c r="D19" s="12">
+      <c r="E19" s="18">
         <v>-30</v>
       </c>
-      <c r="E19" s="13">
+      <c r="F19" s="18">
         <v>-30</v>
       </c>
-      <c r="F19" s="13">
+      <c r="G19" s="18">
         <v>-30</v>
       </c>
-      <c r="G19" s="12">
+      <c r="H19" s="18">
         <v>-30</v>
       </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J19" s="8">
+      <c r="M19" s="8">
         <v>10</v>
       </c>
-      <c r="L19" s="3">
+      <c r="O19" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A20" s="16" t="s">
+    <row r="20" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+      <c r="A20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="18">
         <v>45</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="18">
         <v>40</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="18">
         <v>30</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="18">
         <v>45</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="18">
         <v>40</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="18">
         <v>45</v>
       </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="7" t="s">
+      <c r="H20" s="18">
+        <v>40</v>
+      </c>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J20" s="8">
+      <c r="M20" s="8">
         <v>0</v>
       </c>
-      <c r="L20" s="3">
+      <c r="O20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
+    <row r="21" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+      <c r="A21" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="18">
         <v>135</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="18">
         <v>140</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="18">
         <v>150</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="18">
         <v>135</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="18">
         <v>140</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="18">
         <v>135</v>
       </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="7" t="s">
+      <c r="H21" s="18">
+        <v>140</v>
+      </c>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J21" s="8">
+      <c r="M21" s="8">
         <v>0</v>
       </c>
-      <c r="L21" s="3">
+      <c r="O21" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A22" s="16" t="s">
+    <row r="22" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+      <c r="A22" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="12">
-        <v>600</v>
-      </c>
-      <c r="C22" s="12">
-        <v>600</v>
-      </c>
-      <c r="D22" s="12">
-        <v>600</v>
-      </c>
-      <c r="E22" s="13">
-        <v>600</v>
-      </c>
-      <c r="F22" s="13">
-        <v>600</v>
-      </c>
-      <c r="G22" s="12">
-        <v>600</v>
-      </c>
-      <c r="H22" s="13"/>
-      <c r="I22" s="7" t="s">
+      <c r="B22" s="18">
+        <v>600</v>
+      </c>
+      <c r="C22" s="18">
+        <v>600</v>
+      </c>
+      <c r="D22" s="18">
+        <v>600</v>
+      </c>
+      <c r="E22" s="18">
+        <v>600</v>
+      </c>
+      <c r="F22" s="18">
+        <v>600</v>
+      </c>
+      <c r="G22" s="18">
+        <v>600</v>
+      </c>
+      <c r="H22" s="18">
+        <v>600</v>
+      </c>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J22" s="8">
+      <c r="M22" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A23" s="16" t="s">
+    <row r="23" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+      <c r="A23" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="12">
-        <v>600</v>
-      </c>
-      <c r="C23" s="12">
-        <v>600</v>
-      </c>
-      <c r="D23" s="12">
-        <v>600</v>
-      </c>
-      <c r="E23" s="13">
-        <v>600</v>
-      </c>
-      <c r="F23" s="13">
-        <v>600</v>
-      </c>
-      <c r="G23" s="12">
-        <v>600</v>
-      </c>
-      <c r="H23" s="13"/>
-    </row>
-    <row r="24" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A24" s="16" t="s">
+      <c r="B23" s="18">
+        <v>600</v>
+      </c>
+      <c r="C23" s="18">
+        <v>600</v>
+      </c>
+      <c r="D23" s="18">
+        <v>600</v>
+      </c>
+      <c r="E23" s="18">
+        <v>600</v>
+      </c>
+      <c r="F23" s="18">
+        <v>600</v>
+      </c>
+      <c r="G23" s="18">
+        <v>600</v>
+      </c>
+      <c r="H23" s="18">
+        <v>600</v>
+      </c>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+    </row>
+    <row r="24" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+      <c r="A24" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="12">
-        <v>600</v>
-      </c>
-      <c r="C24" s="12">
-        <v>600</v>
-      </c>
-      <c r="D24" s="12">
-        <v>600</v>
-      </c>
-      <c r="E24" s="13">
-        <v>600</v>
-      </c>
-      <c r="F24" s="13">
-        <v>600</v>
-      </c>
-      <c r="G24" s="12">
-        <v>600</v>
-      </c>
-      <c r="H24" s="13"/>
-    </row>
-    <row r="25" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
+      <c r="B24" s="18">
+        <v>600</v>
+      </c>
+      <c r="C24" s="18">
+        <v>600</v>
+      </c>
+      <c r="D24" s="18">
+        <v>600</v>
+      </c>
+      <c r="E24" s="18">
+        <v>600</v>
+      </c>
+      <c r="F24" s="18">
+        <v>600</v>
+      </c>
+      <c r="G24" s="18">
+        <v>600</v>
+      </c>
+      <c r="H24" s="18">
+        <v>600</v>
+      </c>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+    </row>
+    <row r="25" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+      <c r="A25" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="12">
-        <v>600</v>
-      </c>
-      <c r="C25" s="12">
-        <v>600</v>
-      </c>
-      <c r="D25" s="12">
-        <v>600</v>
-      </c>
-      <c r="E25" s="13">
-        <v>600</v>
-      </c>
-      <c r="F25" s="13">
-        <v>600</v>
-      </c>
-      <c r="G25" s="12">
-        <v>600</v>
-      </c>
-      <c r="H25" s="13"/>
-    </row>
-    <row r="26" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A26" s="16" t="s">
+      <c r="B25" s="18">
+        <v>600</v>
+      </c>
+      <c r="C25" s="18">
+        <v>600</v>
+      </c>
+      <c r="D25" s="18">
+        <v>600</v>
+      </c>
+      <c r="E25" s="18">
+        <v>600</v>
+      </c>
+      <c r="F25" s="18">
+        <v>600</v>
+      </c>
+      <c r="G25" s="18">
+        <v>600</v>
+      </c>
+      <c r="H25" s="18">
+        <v>600</v>
+      </c>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+    </row>
+    <row r="26" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+      <c r="A26" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="12">
-        <v>600</v>
-      </c>
-      <c r="C26" s="12">
-        <v>600</v>
-      </c>
-      <c r="D26" s="12">
-        <v>600</v>
-      </c>
-      <c r="E26" s="13">
-        <v>600</v>
-      </c>
-      <c r="F26" s="13">
-        <v>600</v>
-      </c>
-      <c r="G26" s="12">
-        <v>600</v>
-      </c>
-      <c r="H26" s="13"/>
+      <c r="B26" s="18">
+        <v>600</v>
+      </c>
+      <c r="C26" s="18">
+        <v>600</v>
+      </c>
+      <c r="D26" s="18">
+        <v>600</v>
+      </c>
+      <c r="E26" s="18">
+        <v>600</v>
+      </c>
+      <c r="F26" s="18">
+        <v>600</v>
+      </c>
+      <c r="G26" s="18">
+        <v>600</v>
+      </c>
+      <c r="H26" s="18">
+        <v>600</v>
+      </c>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IndexY\Desktop\paralle_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7DBB0E-6378-46C0-9CE2-C60D6C3FD5C2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15D301A-8BF9-4080-98D1-2067136D346F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -161,7 +161,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>v2</t>
+    <t>v2-0525</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -170,7 +170,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -301,7 +301,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -696,7 +696,9 @@
       <c r="H2" s="18">
         <v>1020</v>
       </c>
-      <c r="I2" s="16"/>
+      <c r="I2" s="18">
+        <v>1020</v>
+      </c>
       <c r="J2" s="16"/>
       <c r="K2" s="16"/>
       <c r="L2" s="1" t="s">
@@ -745,7 +747,9 @@
       <c r="H3" s="18">
         <v>720</v>
       </c>
-      <c r="I3" s="16"/>
+      <c r="I3" s="18">
+        <v>720</v>
+      </c>
       <c r="J3" s="16"/>
       <c r="K3" s="16"/>
       <c r="L3" s="1" t="s">
@@ -794,7 +798,9 @@
       <c r="H4" s="18">
         <v>550</v>
       </c>
-      <c r="I4" s="11"/>
+      <c r="I4" s="18">
+        <v>550</v>
+      </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
       <c r="L4" s="1" t="s">
@@ -843,7 +849,9 @@
       <c r="H5" s="18">
         <v>500</v>
       </c>
-      <c r="I5" s="11"/>
+      <c r="I5" s="18">
+        <v>500</v>
+      </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="1" t="s">
@@ -892,7 +900,9 @@
       <c r="H6" s="18">
         <v>-18</v>
       </c>
-      <c r="I6" s="12"/>
+      <c r="I6" s="18">
+        <v>-2.57</v>
+      </c>
       <c r="J6" s="12"/>
       <c r="K6" s="12"/>
       <c r="L6" s="1" t="s">
@@ -941,7 +951,9 @@
       <c r="H7" s="18">
         <v>150</v>
       </c>
-      <c r="I7" s="12"/>
+      <c r="I7" s="18">
+        <v>148.5</v>
+      </c>
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
       <c r="L7" s="1" t="s">
@@ -990,7 +1002,9 @@
       <c r="H8" s="18">
         <v>40</v>
       </c>
-      <c r="I8" s="12"/>
+      <c r="I8" s="18">
+        <v>62.87</v>
+      </c>
       <c r="J8" s="12"/>
       <c r="K8" s="12"/>
       <c r="L8" s="1" t="s">
@@ -1039,7 +1053,9 @@
       <c r="H9" s="18">
         <v>120</v>
       </c>
-      <c r="I9" s="12"/>
+      <c r="I9" s="18">
+        <v>128</v>
+      </c>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
       <c r="L9" s="1" t="s">
@@ -1088,7 +1104,9 @@
       <c r="H10" s="18">
         <v>150</v>
       </c>
-      <c r="I10" s="14"/>
+      <c r="I10" s="18">
+        <v>150</v>
+      </c>
       <c r="J10" s="14"/>
       <c r="K10" s="14"/>
     </row>
@@ -1117,7 +1135,9 @@
       <c r="H11" s="18">
         <v>155</v>
       </c>
-      <c r="I11" s="14"/>
+      <c r="I11" s="18">
+        <v>155</v>
+      </c>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
       <c r="L11" s="7" t="s">
@@ -1153,7 +1173,9 @@
       <c r="H12" s="18">
         <v>90</v>
       </c>
-      <c r="I12" s="12"/>
+      <c r="I12" s="18">
+        <v>90</v>
+      </c>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
       <c r="L12" s="7" t="s">
@@ -1191,7 +1213,9 @@
       <c r="H13" s="18">
         <v>210</v>
       </c>
-      <c r="I13" s="12"/>
+      <c r="I13" s="18">
+        <v>210</v>
+      </c>
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
       <c r="L13" s="7" t="s">
@@ -1229,7 +1253,9 @@
       <c r="H14" s="18">
         <v>-30</v>
       </c>
-      <c r="I14" s="12"/>
+      <c r="I14" s="18">
+        <v>-30</v>
+      </c>
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
       <c r="L14" s="7" t="s">
@@ -1268,7 +1294,9 @@
       <c r="H15" s="18">
         <v>30</v>
       </c>
-      <c r="I15" s="12"/>
+      <c r="I15" s="18">
+        <v>30</v>
+      </c>
       <c r="J15" s="12"/>
       <c r="K15" s="12"/>
       <c r="L15" s="7" t="s">
@@ -1307,7 +1335,9 @@
       <c r="H16" s="18">
         <v>150</v>
       </c>
-      <c r="I16" s="12"/>
+      <c r="I16" s="18">
+        <v>150</v>
+      </c>
       <c r="J16" s="12"/>
       <c r="K16" s="12"/>
       <c r="L16" s="7" t="s">
@@ -1345,7 +1375,9 @@
       <c r="H17" s="18">
         <v>90</v>
       </c>
-      <c r="I17" s="12"/>
+      <c r="I17" s="18">
+        <v>90</v>
+      </c>
       <c r="J17" s="12"/>
       <c r="K17" s="12"/>
       <c r="L17" s="7" t="s">
@@ -1383,7 +1415,9 @@
       <c r="H18" s="18">
         <v>210</v>
       </c>
-      <c r="I18" s="12"/>
+      <c r="I18" s="18">
+        <v>195</v>
+      </c>
       <c r="J18" s="12"/>
       <c r="K18" s="12"/>
       <c r="L18" s="7" t="s">
@@ -1421,7 +1455,9 @@
       <c r="H19" s="18">
         <v>-30</v>
       </c>
-      <c r="I19" s="12"/>
+      <c r="I19" s="18">
+        <v>-15</v>
+      </c>
       <c r="J19" s="12"/>
       <c r="K19" s="12"/>
       <c r="L19" s="7" t="s">
@@ -1459,7 +1495,9 @@
       <c r="H20" s="18">
         <v>40</v>
       </c>
-      <c r="I20" s="12"/>
+      <c r="I20" s="18">
+        <v>45</v>
+      </c>
       <c r="J20" s="12"/>
       <c r="K20" s="12"/>
       <c r="L20" s="7" t="s">
@@ -1497,7 +1535,9 @@
       <c r="H21" s="18">
         <v>140</v>
       </c>
-      <c r="I21" s="12"/>
+      <c r="I21" s="18">
+        <v>135</v>
+      </c>
       <c r="J21" s="12"/>
       <c r="K21" s="12"/>
       <c r="L21" s="7" t="s">
@@ -1535,7 +1575,9 @@
       <c r="H22" s="18">
         <v>600</v>
       </c>
-      <c r="I22" s="12"/>
+      <c r="I22" s="18">
+        <v>600</v>
+      </c>
       <c r="J22" s="12"/>
       <c r="K22" s="12"/>
       <c r="L22" s="7" t="s">
@@ -1570,7 +1612,9 @@
       <c r="H23" s="18">
         <v>600</v>
       </c>
-      <c r="I23" s="12"/>
+      <c r="I23" s="18">
+        <v>600</v>
+      </c>
       <c r="J23" s="12"/>
       <c r="K23" s="12"/>
     </row>
@@ -1599,7 +1643,9 @@
       <c r="H24" s="18">
         <v>600</v>
       </c>
-      <c r="I24" s="12"/>
+      <c r="I24" s="18">
+        <v>600</v>
+      </c>
       <c r="J24" s="12"/>
       <c r="K24" s="12"/>
     </row>
@@ -1628,7 +1674,9 @@
       <c r="H25" s="18">
         <v>600</v>
       </c>
-      <c r="I25" s="12"/>
+      <c r="I25" s="18">
+        <v>600</v>
+      </c>
       <c r="J25" s="12"/>
       <c r="K25" s="12"/>
     </row>
@@ -1657,7 +1705,9 @@
       <c r="H26" s="18">
         <v>600</v>
       </c>
-      <c r="I26" s="12"/>
+      <c r="I26" s="18">
+        <v>600</v>
+      </c>
       <c r="J26" s="12"/>
       <c r="K26" s="12"/>
     </row>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IndexY\Desktop\paralle_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15D301A-8BF9-4080-98D1-2067136D346F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71ADF07-C74F-4B42-83D9-7CFD917DB1EF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="48">
   <si>
     <t>初始参数</t>
   </si>
@@ -162,6 +162,34 @@
   </si>
   <si>
     <t>v2-0525</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>V3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>V4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>V5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>V6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LTI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LCI</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -207,7 +235,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -222,6 +250,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -260,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -287,13 +321,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -304,6 +332,14 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -609,25 +645,25 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="6" customWidth="1"/>
     <col min="3" max="4" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="11" width="13.5546875" style="5" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.5546875" style="5" customWidth="1"/>
+    <col min="14" max="14" width="12.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -645,1071 +681,1403 @@
       <c r="F1" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="1" t="s">
+      <c r="J1" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="2"/>
-    </row>
-    <row r="2" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="U1" s="2"/>
+    </row>
+    <row r="2" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="16">
         <v>1020</v>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="16">
         <v>1020</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="16">
         <v>1020</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="16">
         <v>2000</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="16">
         <v>2000</v>
       </c>
-      <c r="G2" s="18">
+      <c r="G2" s="16">
         <v>1020</v>
       </c>
-      <c r="H2" s="18">
+      <c r="H2" s="16">
         <v>1020</v>
       </c>
-      <c r="I2" s="18">
+      <c r="I2" s="16">
         <v>1020</v>
       </c>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="1" t="s">
+      <c r="J2" s="16">
+        <v>1020</v>
+      </c>
+      <c r="K2" s="16">
+        <v>1020</v>
+      </c>
+      <c r="L2" s="16">
+        <v>1020</v>
+      </c>
+      <c r="M2" s="18">
+        <v>1020</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="4">
+      <c r="O2" s="4">
         <v>1030</v>
       </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="4">
+      <c r="R2" s="4">
         <v>740</v>
       </c>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1"/>
+      <c r="T2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="4">
+      <c r="U2" s="4">
         <v>740</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="16">
         <v>720</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="16">
         <v>720</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="16">
         <v>720</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="16">
         <v>0</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="16">
         <v>0</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="16">
         <v>720</v>
       </c>
-      <c r="H3" s="18">
+      <c r="H3" s="16">
         <v>720</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="16">
         <v>720</v>
       </c>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="1" t="s">
+      <c r="J3" s="16">
+        <v>720</v>
+      </c>
+      <c r="K3" s="16">
+        <v>720</v>
+      </c>
+      <c r="L3" s="16">
+        <v>720</v>
+      </c>
+      <c r="M3" s="18">
+        <v>720</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="4">
+      <c r="O3" s="4">
         <v>720</v>
       </c>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="4">
+      <c r="R3" s="4">
         <v>570</v>
       </c>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1"/>
+      <c r="T3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="S3" s="4">
+      <c r="U3" s="4">
         <v>570</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="16">
         <v>550</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="16">
         <v>550</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="16">
         <v>550</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="16">
         <v>1281</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="16">
         <v>650</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="16">
         <v>550</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="16">
         <v>550</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="16">
         <v>550</v>
       </c>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="1" t="s">
+      <c r="J4" s="16">
+        <v>550</v>
+      </c>
+      <c r="K4" s="16">
+        <v>550</v>
+      </c>
+      <c r="L4" s="16">
+        <v>550</v>
+      </c>
+      <c r="M4" s="18">
+        <v>550</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="4">
+      <c r="O4" s="4">
         <v>700</v>
       </c>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="P4" s="4">
+      <c r="R4" s="4">
         <v>500</v>
       </c>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1"/>
+      <c r="T4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="S4" s="4">
+      <c r="U4" s="4">
         <v>350</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="16">
         <v>500</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="16">
         <v>500</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="16">
         <v>500</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="16">
         <v>1076</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="16">
         <v>650</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="16">
         <v>550</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="16">
         <v>500</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="16">
         <v>500</v>
       </c>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="1" t="s">
+      <c r="J5" s="16">
+        <v>500</v>
+      </c>
+      <c r="K5" s="16">
+        <v>500</v>
+      </c>
+      <c r="L5" s="16">
+        <v>500</v>
+      </c>
+      <c r="M5" s="18">
+        <v>500</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="4">
-        <v>600</v>
-      </c>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1" t="s">
+      <c r="O5" s="4">
+        <v>600</v>
+      </c>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="4">
+      <c r="R5" s="4">
         <v>450</v>
       </c>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1" t="s">
+      <c r="S5" s="1"/>
+      <c r="T5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="S5" s="4">
+      <c r="U5" s="4">
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="16">
+        <v>25.9</v>
+      </c>
+      <c r="C6" s="16">
+        <v>0</v>
+      </c>
+      <c r="D6" s="16">
+        <v>0</v>
+      </c>
+      <c r="E6" s="16">
+        <v>250</v>
+      </c>
+      <c r="F6" s="16">
+        <v>0</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0</v>
+      </c>
+      <c r="H6" s="16">
+        <v>-18</v>
+      </c>
+      <c r="I6" s="16">
         <v>-2.57</v>
       </c>
-      <c r="C6" s="18">
+      <c r="J6" s="16">
+        <v>4.87</v>
+      </c>
+      <c r="K6" s="16">
         <v>0</v>
       </c>
-      <c r="D6" s="18">
-        <v>0</v>
-      </c>
-      <c r="E6" s="18">
-        <v>250</v>
-      </c>
-      <c r="F6" s="18">
-        <v>0</v>
-      </c>
-      <c r="G6" s="18">
-        <v>0</v>
-      </c>
-      <c r="H6" s="18">
-        <v>-18</v>
-      </c>
-      <c r="I6" s="18">
-        <v>-2.57</v>
-      </c>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="16">
+        <v>25.9</v>
+      </c>
+      <c r="M6" s="18">
+        <v>17.3</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M6" s="4">
+      <c r="O6" s="4">
         <v>-60</v>
       </c>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1" t="s">
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="P6" s="4">
+      <c r="R6" s="4">
         <v>-45</v>
       </c>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1" t="s">
+      <c r="S6" s="1"/>
+      <c r="T6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="S6" s="4">
+      <c r="U6" s="4">
         <v>-30</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="16">
+        <v>175.47</v>
+      </c>
+      <c r="C7" s="16">
+        <v>150</v>
+      </c>
+      <c r="D7" s="16">
+        <v>100</v>
+      </c>
+      <c r="E7" s="16">
+        <v>180</v>
+      </c>
+      <c r="F7" s="16">
+        <v>180</v>
+      </c>
+      <c r="G7" s="16">
+        <v>150</v>
+      </c>
+      <c r="H7" s="16">
+        <v>150</v>
+      </c>
+      <c r="I7" s="16">
         <v>148.5</v>
       </c>
-      <c r="C7" s="18">
-        <v>150</v>
-      </c>
-      <c r="D7" s="18">
-        <v>100</v>
-      </c>
-      <c r="E7" s="18">
-        <v>180</v>
-      </c>
-      <c r="F7" s="18">
-        <v>180</v>
-      </c>
-      <c r="G7" s="18">
-        <v>150</v>
-      </c>
-      <c r="H7" s="18">
-        <v>150</v>
-      </c>
-      <c r="I7" s="18">
-        <v>148.5</v>
-      </c>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="1" t="s">
+      <c r="J7" s="16">
+        <v>120.94</v>
+      </c>
+      <c r="K7" s="16">
+        <v>126.26</v>
+      </c>
+      <c r="L7" s="16">
+        <v>175.47</v>
+      </c>
+      <c r="M7" s="18">
+        <v>176.69</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="4">
+      <c r="O7" s="4">
         <v>120</v>
       </c>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1" t="s">
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="P7" s="4">
+      <c r="R7" s="4">
         <v>80</v>
       </c>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1" t="s">
+      <c r="S7" s="1"/>
+      <c r="T7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="S7" s="4">
+      <c r="U7" s="4">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="16">
+        <v>67.22</v>
+      </c>
+      <c r="C8" s="16">
+        <v>80</v>
+      </c>
+      <c r="D8" s="16">
+        <v>80</v>
+      </c>
+      <c r="E8" s="16">
+        <v>180</v>
+      </c>
+      <c r="F8" s="16">
+        <v>90</v>
+      </c>
+      <c r="G8" s="16">
+        <v>75</v>
+      </c>
+      <c r="H8" s="16">
+        <v>40</v>
+      </c>
+      <c r="I8" s="16">
         <v>62.87</v>
       </c>
-      <c r="C8" s="18">
-        <v>80</v>
-      </c>
-      <c r="D8" s="18">
-        <v>80</v>
-      </c>
-      <c r="E8" s="18">
-        <v>180</v>
-      </c>
-      <c r="F8" s="18">
-        <v>90</v>
-      </c>
-      <c r="G8" s="18">
-        <v>75</v>
-      </c>
-      <c r="H8" s="18">
-        <v>40</v>
-      </c>
-      <c r="I8" s="18">
-        <v>62.87</v>
-      </c>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="1" t="s">
+      <c r="J8" s="16">
+        <v>61.47</v>
+      </c>
+      <c r="K8" s="16">
+        <v>62.27</v>
+      </c>
+      <c r="L8" s="16">
+        <v>67.22</v>
+      </c>
+      <c r="M8" s="18">
+        <v>66.83</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M8" s="4">
+      <c r="O8" s="4">
         <v>100</v>
       </c>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1" t="s">
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="P8" s="4">
+      <c r="R8" s="4">
         <v>70</v>
       </c>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1" t="s">
+      <c r="S8" s="1"/>
+      <c r="T8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="S8" s="4">
+      <c r="U8" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="16">
+        <v>174.33</v>
+      </c>
+      <c r="C9" s="16">
+        <v>315</v>
+      </c>
+      <c r="D9" s="16">
+        <v>10</v>
+      </c>
+      <c r="E9" s="16">
+        <v>340</v>
+      </c>
+      <c r="F9" s="16">
+        <v>370</v>
+      </c>
+      <c r="G9" s="16">
+        <v>315</v>
+      </c>
+      <c r="H9" s="16">
+        <v>120</v>
+      </c>
+      <c r="I9" s="16">
         <v>128</v>
       </c>
-      <c r="C9" s="18">
-        <v>315</v>
-      </c>
-      <c r="D9" s="18">
+      <c r="J9" s="16">
+        <v>121.69</v>
+      </c>
+      <c r="K9" s="16">
+        <v>116.6</v>
+      </c>
+      <c r="L9" s="16">
+        <v>174.33</v>
+      </c>
+      <c r="M9" s="18">
+        <v>166.77</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="18">
-        <v>340</v>
-      </c>
-      <c r="F9" s="18">
-        <v>370</v>
-      </c>
-      <c r="G9" s="18">
-        <v>315</v>
-      </c>
-      <c r="H9" s="18">
-        <v>120</v>
-      </c>
-      <c r="I9" s="18">
-        <v>128</v>
-      </c>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="1" t="s">
+      <c r="O9" s="4">
+        <v>20</v>
+      </c>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M9" s="4">
-        <v>20</v>
-      </c>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1" t="s">
+      <c r="R9" s="4">
         <v>10</v>
       </c>
-      <c r="P9" s="4">
+      <c r="S9" s="1"/>
+      <c r="T9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1" t="s">
+      <c r="U9" s="4">
         <v>10</v>
       </c>
-      <c r="S9" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="15" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+    </row>
+    <row r="10" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="18">
-        <v>150</v>
-      </c>
-      <c r="C10" s="18">
-        <v>150</v>
-      </c>
-      <c r="D10" s="18">
-        <v>150</v>
-      </c>
-      <c r="E10" s="18">
+      <c r="B10" s="16">
+        <v>150</v>
+      </c>
+      <c r="C10" s="16">
+        <v>150</v>
+      </c>
+      <c r="D10" s="16">
+        <v>150</v>
+      </c>
+      <c r="E10" s="16">
         <v>0</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="16">
         <v>220</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="16">
         <v>140</v>
       </c>
-      <c r="H10" s="18">
-        <v>150</v>
-      </c>
-      <c r="I10" s="18">
-        <v>150</v>
-      </c>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-    </row>
-    <row r="11" spans="1:19" ht="15" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
+      <c r="H10" s="16">
+        <v>150</v>
+      </c>
+      <c r="I10" s="16">
+        <v>150</v>
+      </c>
+      <c r="J10" s="16">
+        <v>150</v>
+      </c>
+      <c r="K10" s="16">
+        <v>150</v>
+      </c>
+      <c r="L10" s="16">
+        <v>150</v>
+      </c>
+      <c r="M10" s="18">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="16">
         <v>155</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="16">
         <v>155</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="16">
         <v>155</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="16">
         <v>155</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="16">
         <v>155</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="16">
         <v>155</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="16">
         <v>155</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="16">
         <v>155</v>
       </c>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="7" t="s">
+      <c r="J11" s="16">
+        <v>155</v>
+      </c>
+      <c r="K11" s="16">
+        <v>155</v>
+      </c>
+      <c r="L11" s="16">
+        <v>155</v>
+      </c>
+      <c r="M11" s="18">
+        <v>155</v>
+      </c>
+      <c r="N11" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="8"/>
-      <c r="O11" s="3">
+      <c r="O11" s="8"/>
+      <c r="Q11" s="3">
         <v>1020</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+    <row r="12" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="18">
-        <v>90</v>
-      </c>
-      <c r="C12" s="18">
-        <v>90</v>
-      </c>
-      <c r="D12" s="18">
-        <v>90</v>
-      </c>
-      <c r="E12" s="18">
-        <v>90</v>
-      </c>
-      <c r="F12" s="18">
-        <v>90</v>
-      </c>
-      <c r="G12" s="18">
-        <v>90</v>
-      </c>
-      <c r="H12" s="18">
-        <v>90</v>
-      </c>
-      <c r="I12" s="18">
-        <v>90</v>
-      </c>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="7" t="s">
+      <c r="B12" s="16">
+        <v>90</v>
+      </c>
+      <c r="C12" s="16">
+        <v>90</v>
+      </c>
+      <c r="D12" s="16">
+        <v>90</v>
+      </c>
+      <c r="E12" s="16">
+        <v>90</v>
+      </c>
+      <c r="F12" s="16">
+        <v>90</v>
+      </c>
+      <c r="G12" s="16">
+        <v>90</v>
+      </c>
+      <c r="H12" s="16">
+        <v>90</v>
+      </c>
+      <c r="I12" s="16">
+        <v>90</v>
+      </c>
+      <c r="J12" s="16">
+        <v>90</v>
+      </c>
+      <c r="K12" s="16">
+        <v>90</v>
+      </c>
+      <c r="L12" s="16">
+        <v>90</v>
+      </c>
+      <c r="M12" s="18">
+        <v>90</v>
+      </c>
+      <c r="N12" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="8">
+      <c r="O12" s="8">
         <v>1030</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>730</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="15" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+    <row r="13" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="16">
         <v>210</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="16">
         <v>210</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="16">
         <v>210</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="16">
         <v>210</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="16">
         <v>210</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="16">
         <v>210</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="16">
         <v>210</v>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="16">
         <v>210</v>
       </c>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="7" t="s">
+      <c r="J13" s="16">
+        <v>210</v>
+      </c>
+      <c r="K13" s="16">
+        <v>210</v>
+      </c>
+      <c r="L13" s="16">
+        <v>210</v>
+      </c>
+      <c r="M13" s="18">
+        <v>210</v>
+      </c>
+      <c r="N13" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="M13" s="8">
+      <c r="O13" s="8">
         <v>720</v>
       </c>
-      <c r="O13" s="3">
+      <c r="Q13" s="3">
         <v>550</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="15" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+    <row r="14" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="16">
         <v>-30</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="16">
         <v>-30</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="16">
         <v>-30</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="16">
         <v>-30</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="16">
         <v>-30</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="16">
         <v>-30</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="16">
         <v>-30</v>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="16">
         <v>-30</v>
       </c>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="7" t="s">
+      <c r="J14" s="16">
+        <v>-30</v>
+      </c>
+      <c r="K14" s="16">
+        <v>-30</v>
+      </c>
+      <c r="L14" s="16">
+        <v>-30</v>
+      </c>
+      <c r="M14" s="18">
+        <v>-30</v>
+      </c>
+      <c r="N14" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="8">
+      <c r="O14" s="8">
         <v>550</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="15" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
+    <row r="15" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="16">
         <v>30</v>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="16">
         <v>30</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="16">
         <v>30</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="16">
         <v>50</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="16">
         <f>90-33.3</f>
         <v>56.7</v>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="16">
         <v>45</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="16">
         <v>30</v>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="16">
         <v>30</v>
       </c>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="7" t="s">
+      <c r="J15" s="16">
+        <v>30</v>
+      </c>
+      <c r="K15" s="16">
+        <v>30</v>
+      </c>
+      <c r="L15" s="16">
+        <v>30</v>
+      </c>
+      <c r="M15" s="18">
+        <v>30</v>
+      </c>
+      <c r="N15" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="8">
+      <c r="O15" s="8">
         <v>500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="15" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
+    <row r="16" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="18">
-        <v>150</v>
-      </c>
-      <c r="C16" s="18">
-        <v>150</v>
-      </c>
-      <c r="D16" s="18">
-        <v>150</v>
-      </c>
-      <c r="E16" s="18">
+      <c r="B16" s="16">
+        <v>150</v>
+      </c>
+      <c r="C16" s="16">
+        <v>150</v>
+      </c>
+      <c r="D16" s="16">
+        <v>150</v>
+      </c>
+      <c r="E16" s="16">
         <v>130</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="16">
         <f>90+33.3</f>
         <v>123.3</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="16">
         <v>135</v>
       </c>
-      <c r="H16" s="18">
-        <v>150</v>
-      </c>
-      <c r="I16" s="18">
-        <v>150</v>
-      </c>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="7" t="s">
+      <c r="H16" s="16">
+        <v>150</v>
+      </c>
+      <c r="I16" s="16">
+        <v>150</v>
+      </c>
+      <c r="J16" s="16">
+        <v>150</v>
+      </c>
+      <c r="K16" s="16">
+        <v>150</v>
+      </c>
+      <c r="L16" s="16">
+        <v>150</v>
+      </c>
+      <c r="M16" s="18">
+        <v>150</v>
+      </c>
+      <c r="N16" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="M16" s="8">
+      <c r="O16" s="8">
         <v>0</v>
       </c>
-      <c r="O16" s="3">
+      <c r="Q16" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
+    <row r="17" spans="1:17" ht="15" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18">
-        <v>90</v>
-      </c>
-      <c r="C17" s="18">
-        <v>90</v>
-      </c>
-      <c r="D17" s="18">
-        <v>90</v>
-      </c>
-      <c r="E17" s="18">
-        <v>90</v>
-      </c>
-      <c r="F17" s="18">
-        <v>90</v>
-      </c>
-      <c r="G17" s="18">
-        <v>90</v>
-      </c>
-      <c r="H17" s="18">
-        <v>90</v>
-      </c>
-      <c r="I17" s="18">
-        <v>90</v>
-      </c>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="7" t="s">
+      <c r="B17" s="16">
+        <v>90</v>
+      </c>
+      <c r="C17" s="16">
+        <v>90</v>
+      </c>
+      <c r="D17" s="16">
+        <v>90</v>
+      </c>
+      <c r="E17" s="16">
+        <v>90</v>
+      </c>
+      <c r="F17" s="16">
+        <v>90</v>
+      </c>
+      <c r="G17" s="16">
+        <v>90</v>
+      </c>
+      <c r="H17" s="16">
+        <v>90</v>
+      </c>
+      <c r="I17" s="16">
+        <v>90</v>
+      </c>
+      <c r="J17" s="16">
+        <v>90</v>
+      </c>
+      <c r="K17" s="16">
+        <v>90</v>
+      </c>
+      <c r="L17" s="16">
+        <v>90</v>
+      </c>
+      <c r="M17" s="18">
+        <v>90</v>
+      </c>
+      <c r="N17" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="M17" s="8">
+      <c r="O17" s="8">
         <v>100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+    <row r="18" spans="1:17" ht="15" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="16">
+        <f>270-69.7</f>
+        <v>200.3</v>
+      </c>
+      <c r="C18" s="16">
+        <v>210</v>
+      </c>
+      <c r="D18" s="16">
+        <v>210</v>
+      </c>
+      <c r="E18" s="16">
+        <v>210</v>
+      </c>
+      <c r="F18" s="16">
+        <v>210</v>
+      </c>
+      <c r="G18" s="16">
+        <v>210</v>
+      </c>
+      <c r="H18" s="16">
+        <v>210</v>
+      </c>
+      <c r="I18" s="16">
         <v>195</v>
       </c>
-      <c r="C18" s="18">
-        <v>210</v>
-      </c>
-      <c r="D18" s="18">
-        <v>210</v>
-      </c>
-      <c r="E18" s="18">
-        <v>210</v>
-      </c>
-      <c r="F18" s="18">
-        <v>210</v>
-      </c>
-      <c r="G18" s="18">
-        <v>210</v>
-      </c>
-      <c r="H18" s="18">
-        <v>210</v>
-      </c>
-      <c r="I18" s="18">
-        <v>195</v>
-      </c>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="7" t="s">
+      <c r="J18" s="16">
+        <f>270-80</f>
+        <v>190</v>
+      </c>
+      <c r="K18" s="16">
+        <f>270-80</f>
+        <v>190</v>
+      </c>
+      <c r="L18" s="16">
+        <f>270-69.7</f>
+        <v>200.3</v>
+      </c>
+      <c r="M18" s="18">
+        <f>270-70</f>
+        <v>200</v>
+      </c>
+      <c r="N18" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M18" s="8">
+      <c r="O18" s="8">
         <v>80</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+    <row r="19" spans="1:17" ht="15" x14ac:dyDescent="0.3">
+      <c r="A19" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="16">
+        <f>-90+69.7</f>
+        <v>-20.299999999999997</v>
+      </c>
+      <c r="C19" s="16">
+        <v>-30</v>
+      </c>
+      <c r="D19" s="16">
+        <v>-30</v>
+      </c>
+      <c r="E19" s="16">
+        <v>-30</v>
+      </c>
+      <c r="F19" s="16">
+        <v>-30</v>
+      </c>
+      <c r="G19" s="16">
+        <v>-30</v>
+      </c>
+      <c r="H19" s="16">
+        <v>-30</v>
+      </c>
+      <c r="I19" s="16">
         <v>-15</v>
       </c>
-      <c r="C19" s="18">
-        <v>-30</v>
-      </c>
-      <c r="D19" s="18">
-        <v>-30</v>
-      </c>
-      <c r="E19" s="18">
-        <v>-30</v>
-      </c>
-      <c r="F19" s="18">
-        <v>-30</v>
-      </c>
-      <c r="G19" s="18">
-        <v>-30</v>
-      </c>
-      <c r="H19" s="18">
-        <v>-30</v>
-      </c>
-      <c r="I19" s="18">
-        <v>-15</v>
-      </c>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="7" t="s">
+      <c r="J19" s="16">
+        <f>-90+80</f>
+        <v>-10</v>
+      </c>
+      <c r="K19" s="16">
+        <f>-90+80</f>
+        <v>-10</v>
+      </c>
+      <c r="L19" s="16">
+        <f>-90+69.7</f>
+        <v>-20.299999999999997</v>
+      </c>
+      <c r="M19" s="18">
+        <f>-90+70</f>
+        <v>-20</v>
+      </c>
+      <c r="N19" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="M19" s="8">
+      <c r="O19" s="8">
         <v>10</v>
       </c>
-      <c r="O19" s="3">
+      <c r="Q19" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
+    <row r="20" spans="1:17" ht="15" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="16">
+        <f>90-42.66</f>
+        <v>47.34</v>
+      </c>
+      <c r="C20" s="16">
+        <v>40</v>
+      </c>
+      <c r="D20" s="16">
+        <v>30</v>
+      </c>
+      <c r="E20" s="16">
         <v>45</v>
       </c>
-      <c r="C20" s="18">
+      <c r="F20" s="16">
         <v>40</v>
       </c>
-      <c r="D20" s="18">
+      <c r="G20" s="16">
+        <v>45</v>
+      </c>
+      <c r="H20" s="16">
+        <v>40</v>
+      </c>
+      <c r="I20" s="16">
+        <v>45</v>
+      </c>
+      <c r="J20" s="16">
+        <f>90-43.6</f>
+        <v>46.4</v>
+      </c>
+      <c r="K20" s="16">
+        <f>90-46.9</f>
+        <v>43.1</v>
+      </c>
+      <c r="L20" s="16">
+        <f>90-42.66</f>
+        <v>47.34</v>
+      </c>
+      <c r="M20" s="18">
+        <f>90-43.4</f>
+        <v>46.6</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="O20" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="15" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="16">
+        <f>90+42.66</f>
+        <v>132.66</v>
+      </c>
+      <c r="C21" s="16">
+        <v>140</v>
+      </c>
+      <c r="D21" s="16">
+        <v>150</v>
+      </c>
+      <c r="E21" s="16">
+        <v>135</v>
+      </c>
+      <c r="F21" s="16">
+        <v>140</v>
+      </c>
+      <c r="G21" s="16">
+        <v>135</v>
+      </c>
+      <c r="H21" s="16">
+        <v>140</v>
+      </c>
+      <c r="I21" s="16">
+        <v>135</v>
+      </c>
+      <c r="J21" s="16">
+        <f>90+43.6</f>
+        <v>133.6</v>
+      </c>
+      <c r="K21" s="16">
+        <f>90+46.9</f>
+        <v>136.9</v>
+      </c>
+      <c r="L21" s="16">
+        <f>90+42.66</f>
+        <v>132.66</v>
+      </c>
+      <c r="M21" s="18">
+        <f>90+43.4</f>
+        <v>133.4</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="O21" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="15" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="16">
+        <v>600</v>
+      </c>
+      <c r="C22" s="16">
+        <v>600</v>
+      </c>
+      <c r="D22" s="16">
+        <v>600</v>
+      </c>
+      <c r="E22" s="16">
+        <v>600</v>
+      </c>
+      <c r="F22" s="16">
+        <v>600</v>
+      </c>
+      <c r="G22" s="16">
+        <v>600</v>
+      </c>
+      <c r="H22" s="16">
+        <v>600</v>
+      </c>
+      <c r="I22" s="16">
+        <v>600</v>
+      </c>
+      <c r="J22" s="16">
+        <v>600</v>
+      </c>
+      <c r="K22" s="16">
+        <v>600</v>
+      </c>
+      <c r="L22" s="16">
+        <v>600</v>
+      </c>
+      <c r="M22" s="18">
+        <v>600</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="O22" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="15" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="16">
+        <v>600</v>
+      </c>
+      <c r="C23" s="16">
+        <v>600</v>
+      </c>
+      <c r="D23" s="16">
+        <v>600</v>
+      </c>
+      <c r="E23" s="16">
+        <v>600</v>
+      </c>
+      <c r="F23" s="16">
+        <v>600</v>
+      </c>
+      <c r="G23" s="16">
+        <v>600</v>
+      </c>
+      <c r="H23" s="16">
+        <v>600</v>
+      </c>
+      <c r="I23" s="16">
+        <v>600</v>
+      </c>
+      <c r="J23" s="16">
+        <v>600</v>
+      </c>
+      <c r="K23" s="16">
+        <v>600</v>
+      </c>
+      <c r="L23" s="16">
+        <v>600</v>
+      </c>
+      <c r="M23" s="18">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="15" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="16">
+        <v>600</v>
+      </c>
+      <c r="C24" s="16">
+        <v>600</v>
+      </c>
+      <c r="D24" s="16">
+        <v>600</v>
+      </c>
+      <c r="E24" s="16">
+        <v>600</v>
+      </c>
+      <c r="F24" s="16">
+        <v>600</v>
+      </c>
+      <c r="G24" s="16">
+        <v>600</v>
+      </c>
+      <c r="H24" s="16">
+        <v>600</v>
+      </c>
+      <c r="I24" s="16">
+        <v>600</v>
+      </c>
+      <c r="J24" s="16">
+        <v>600</v>
+      </c>
+      <c r="K24" s="16">
+        <v>600</v>
+      </c>
+      <c r="L24" s="16">
+        <v>600</v>
+      </c>
+      <c r="M24" s="18">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="15" x14ac:dyDescent="0.3">
+      <c r="A25" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="16">
+        <v>600</v>
+      </c>
+      <c r="C25" s="16">
+        <v>600</v>
+      </c>
+      <c r="D25" s="16">
+        <v>600</v>
+      </c>
+      <c r="E25" s="16">
+        <v>600</v>
+      </c>
+      <c r="F25" s="16">
+        <v>600</v>
+      </c>
+      <c r="G25" s="16">
+        <v>600</v>
+      </c>
+      <c r="H25" s="16">
+        <v>600</v>
+      </c>
+      <c r="I25" s="16">
+        <v>600</v>
+      </c>
+      <c r="J25" s="16">
+        <v>600</v>
+      </c>
+      <c r="K25" s="16">
+        <v>600</v>
+      </c>
+      <c r="L25" s="16">
+        <v>600</v>
+      </c>
+      <c r="M25" s="18">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="15" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="18">
+      <c r="B26" s="16">
+        <v>600</v>
+      </c>
+      <c r="C26" s="16">
+        <v>600</v>
+      </c>
+      <c r="D26" s="16">
+        <v>600</v>
+      </c>
+      <c r="E26" s="16">
+        <v>600</v>
+      </c>
+      <c r="F26" s="16">
+        <v>600</v>
+      </c>
+      <c r="G26" s="16">
+        <v>600</v>
+      </c>
+      <c r="H26" s="16">
+        <v>600</v>
+      </c>
+      <c r="I26" s="16">
+        <v>600</v>
+      </c>
+      <c r="J26" s="16">
+        <v>600</v>
+      </c>
+      <c r="K26" s="16">
+        <v>600</v>
+      </c>
+      <c r="L26" s="16">
+        <v>600</v>
+      </c>
+      <c r="M26" s="18">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15" x14ac:dyDescent="0.3">
+      <c r="A27" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="18">
-        <v>40</v>
-      </c>
-      <c r="G20" s="18">
-        <v>45</v>
-      </c>
-      <c r="H20" s="18">
-        <v>40</v>
-      </c>
-      <c r="I20" s="18">
-        <v>45</v>
-      </c>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M20" s="8">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="15" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="18">
-        <v>135</v>
-      </c>
-      <c r="C21" s="18">
-        <v>140</v>
-      </c>
-      <c r="D21" s="18">
-        <v>150</v>
-      </c>
-      <c r="E21" s="18">
-        <v>135</v>
-      </c>
-      <c r="F21" s="18">
-        <v>140</v>
-      </c>
-      <c r="G21" s="18">
-        <v>135</v>
-      </c>
-      <c r="H21" s="18">
-        <v>140</v>
-      </c>
-      <c r="I21" s="18">
-        <v>135</v>
-      </c>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="M21" s="8">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="15" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="18">
-        <v>600</v>
-      </c>
-      <c r="C22" s="18">
-        <v>600</v>
-      </c>
-      <c r="D22" s="18">
-        <v>600</v>
-      </c>
-      <c r="E22" s="18">
-        <v>600</v>
-      </c>
-      <c r="F22" s="18">
-        <v>600</v>
-      </c>
-      <c r="G22" s="18">
-        <v>600</v>
-      </c>
-      <c r="H22" s="18">
-        <v>600</v>
-      </c>
-      <c r="I22" s="18">
-        <v>600</v>
-      </c>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M22" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="15" x14ac:dyDescent="0.3">
-      <c r="A23" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="18">
-        <v>600</v>
-      </c>
-      <c r="C23" s="18">
-        <v>600</v>
-      </c>
-      <c r="D23" s="18">
-        <v>600</v>
-      </c>
-      <c r="E23" s="18">
-        <v>600</v>
-      </c>
-      <c r="F23" s="18">
-        <v>600</v>
-      </c>
-      <c r="G23" s="18">
-        <v>600</v>
-      </c>
-      <c r="H23" s="18">
-        <v>600</v>
-      </c>
-      <c r="I23" s="18">
-        <v>600</v>
-      </c>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-    </row>
-    <row r="24" spans="1:15" ht="15" x14ac:dyDescent="0.3">
-      <c r="A24" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="18">
-        <v>600</v>
-      </c>
-      <c r="C24" s="18">
-        <v>600</v>
-      </c>
-      <c r="D24" s="18">
-        <v>600</v>
-      </c>
-      <c r="E24" s="18">
-        <v>600</v>
-      </c>
-      <c r="F24" s="18">
-        <v>600</v>
-      </c>
-      <c r="G24" s="18">
-        <v>600</v>
-      </c>
-      <c r="H24" s="18">
-        <v>600</v>
-      </c>
-      <c r="I24" s="18">
-        <v>600</v>
-      </c>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-    </row>
-    <row r="25" spans="1:15" ht="15" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="18">
-        <v>600</v>
-      </c>
-      <c r="C25" s="18">
-        <v>600</v>
-      </c>
-      <c r="D25" s="18">
-        <v>600</v>
-      </c>
-      <c r="E25" s="18">
-        <v>600</v>
-      </c>
-      <c r="F25" s="18">
-        <v>600</v>
-      </c>
-      <c r="G25" s="18">
-        <v>600</v>
-      </c>
-      <c r="H25" s="18">
-        <v>600</v>
-      </c>
-      <c r="I25" s="18">
-        <v>600</v>
-      </c>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-    </row>
-    <row r="26" spans="1:15" ht="15" x14ac:dyDescent="0.3">
-      <c r="A26" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="18">
-        <v>600</v>
-      </c>
-      <c r="C26" s="18">
-        <v>600</v>
-      </c>
-      <c r="D26" s="18">
-        <v>600</v>
-      </c>
-      <c r="E26" s="18">
-        <v>600</v>
-      </c>
-      <c r="F26" s="18">
-        <v>600</v>
-      </c>
-      <c r="G26" s="18">
-        <v>600</v>
-      </c>
-      <c r="H26" s="18">
-        <v>600</v>
-      </c>
-      <c r="I26" s="18">
-        <v>600</v>
-      </c>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
+      <c r="I27" s="5">
+        <v>0.48846277999999999</v>
+      </c>
+      <c r="J27" s="5">
+        <v>0.48888725999999999</v>
+      </c>
+      <c r="K27" s="5">
+        <v>0.49539560999999999</v>
+      </c>
+      <c r="L27" s="5">
+        <v>0.48496798000000002</v>
+      </c>
+      <c r="M27" s="19">
+        <v>0.4857378</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I28" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M28" s="19"/>
+    </row>
+    <row r="29" spans="1:17" ht="15" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I29" s="5">
+        <v>5.0462090000000001E-2</v>
+      </c>
+      <c r="J29" s="5">
+        <v>4.3018510000000003E-2</v>
+      </c>
+      <c r="K29" s="17">
+        <v>4.4411949999999999E-2</v>
+      </c>
+      <c r="L29" s="5">
+        <v>5.9470200000000001E-2</v>
+      </c>
+      <c r="M29" s="19">
+        <v>5.9116960000000003E-2</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IndexY\Desktop\paralle_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71ADF07-C74F-4B42-83D9-7CFD917DB1EF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592D2456-DD10-4BFE-83DC-4A67D56F5B95}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -235,7 +235,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,6 +256,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -294,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -340,6 +352,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -687,7 +706,7 @@
       <c r="H1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="22" t="s">
         <v>40</v>
       </c>
       <c r="J1" s="14" t="s">
@@ -742,7 +761,7 @@
       <c r="H2" s="16">
         <v>1020</v>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="18">
         <v>1020</v>
       </c>
       <c r="J2" s="16">
@@ -803,7 +822,7 @@
       <c r="H3" s="16">
         <v>720</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="18">
         <v>720</v>
       </c>
       <c r="J3" s="16">
@@ -864,7 +883,7 @@
       <c r="H4" s="16">
         <v>550</v>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="18">
         <v>550</v>
       </c>
       <c r="J4" s="16">
@@ -925,7 +944,7 @@
       <c r="H5" s="16">
         <v>500</v>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="18">
         <v>500</v>
       </c>
       <c r="J5" s="16">
@@ -966,7 +985,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="16">
-        <v>25.9</v>
+        <v>-2.57</v>
       </c>
       <c r="C6" s="16">
         <v>0</v>
@@ -986,7 +1005,7 @@
       <c r="H6" s="16">
         <v>-18</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="18">
         <v>-2.57</v>
       </c>
       <c r="J6" s="16">
@@ -1027,7 +1046,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="16">
-        <v>175.47</v>
+        <v>148.5</v>
       </c>
       <c r="C7" s="16">
         <v>150</v>
@@ -1047,7 +1066,7 @@
       <c r="H7" s="16">
         <v>150</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="18">
         <v>148.5</v>
       </c>
       <c r="J7" s="16">
@@ -1088,7 +1107,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="16">
-        <v>67.22</v>
+        <v>62.87</v>
       </c>
       <c r="C8" s="16">
         <v>80</v>
@@ -1108,7 +1127,7 @@
       <c r="H8" s="16">
         <v>40</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="18">
         <v>62.87</v>
       </c>
       <c r="J8" s="16">
@@ -1149,7 +1168,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="16">
-        <v>174.33</v>
+        <v>128</v>
       </c>
       <c r="C9" s="16">
         <v>315</v>
@@ -1169,7 +1188,7 @@
       <c r="H9" s="16">
         <v>120</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="21">
         <v>128</v>
       </c>
       <c r="J9" s="16">
@@ -1181,7 +1200,7 @@
       <c r="L9" s="16">
         <v>174.33</v>
       </c>
-      <c r="M9" s="18">
+      <c r="M9" s="21">
         <v>166.77</v>
       </c>
       <c r="N9" s="1" t="s">
@@ -1230,7 +1249,7 @@
       <c r="H10" s="16">
         <v>150</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="18">
         <v>150</v>
       </c>
       <c r="J10" s="16">
@@ -1271,7 +1290,7 @@
       <c r="H11" s="16">
         <v>155</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="18">
         <v>155</v>
       </c>
       <c r="J11" s="16">
@@ -1319,7 +1338,7 @@
       <c r="H12" s="16">
         <v>90</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="18">
         <v>90</v>
       </c>
       <c r="J12" s="16">
@@ -1369,7 +1388,7 @@
       <c r="H13" s="16">
         <v>210</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="18">
         <v>210</v>
       </c>
       <c r="J13" s="16">
@@ -1419,7 +1438,7 @@
       <c r="H14" s="16">
         <v>-30</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="18">
         <v>-30</v>
       </c>
       <c r="J14" s="16">
@@ -1470,7 +1489,7 @@
       <c r="H15" s="16">
         <v>30</v>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="18">
         <v>30</v>
       </c>
       <c r="J15" s="16">
@@ -1521,7 +1540,7 @@
       <c r="H16" s="16">
         <v>150</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="18">
         <v>150</v>
       </c>
       <c r="J16" s="16">
@@ -1571,7 +1590,7 @@
       <c r="H17" s="16">
         <v>90</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="18">
         <v>90</v>
       </c>
       <c r="J17" s="16">
@@ -1601,8 +1620,7 @@
         <v>22</v>
       </c>
       <c r="B18" s="16">
-        <f>270-69.7</f>
-        <v>200.3</v>
+        <v>195</v>
       </c>
       <c r="C18" s="16">
         <v>210</v>
@@ -1622,7 +1640,7 @@
       <c r="H18" s="16">
         <v>210</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="18">
         <v>195</v>
       </c>
       <c r="J18" s="16">
@@ -1656,8 +1674,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="16">
-        <f>-90+69.7</f>
-        <v>-20.299999999999997</v>
+        <v>-15</v>
       </c>
       <c r="C19" s="16">
         <v>-30</v>
@@ -1677,7 +1694,7 @@
       <c r="H19" s="16">
         <v>-30</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="21">
         <v>-15</v>
       </c>
       <c r="J19" s="16">
@@ -1692,7 +1709,7 @@
         <f>-90+69.7</f>
         <v>-20.299999999999997</v>
       </c>
-      <c r="M19" s="18">
+      <c r="M19" s="21">
         <f>-90+70</f>
         <v>-20</v>
       </c>
@@ -1711,8 +1728,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="16">
-        <f>90-42.66</f>
-        <v>47.34</v>
+        <v>45</v>
       </c>
       <c r="C20" s="16">
         <v>40</v>
@@ -1732,7 +1748,7 @@
       <c r="H20" s="16">
         <v>40</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="18">
         <v>45</v>
       </c>
       <c r="J20" s="16">
@@ -1766,8 +1782,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="16">
-        <f>90+42.66</f>
-        <v>132.66</v>
+        <v>135</v>
       </c>
       <c r="C21" s="16">
         <v>140</v>
@@ -1787,7 +1802,7 @@
       <c r="H21" s="16">
         <v>140</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="18">
         <v>135</v>
       </c>
       <c r="J21" s="16">
@@ -1841,7 +1856,7 @@
       <c r="H22" s="16">
         <v>600</v>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="18">
         <v>600</v>
       </c>
       <c r="J22" s="16">
@@ -1888,7 +1903,7 @@
       <c r="H23" s="16">
         <v>600</v>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="18">
         <v>600</v>
       </c>
       <c r="J23" s="16">
@@ -1929,7 +1944,7 @@
       <c r="H24" s="16">
         <v>600</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="18">
         <v>600</v>
       </c>
       <c r="J24" s="16">
@@ -1970,7 +1985,7 @@
       <c r="H25" s="16">
         <v>600</v>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="18">
         <v>600</v>
       </c>
       <c r="J25" s="16">
@@ -2011,7 +2026,7 @@
       <c r="H26" s="16">
         <v>600</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="18">
         <v>600</v>
       </c>
       <c r="J26" s="16">
@@ -2031,7 +2046,10 @@
       <c r="A27" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I27" s="5">
+      <c r="B27" s="23">
+        <v>0.48061528999999997</v>
+      </c>
+      <c r="I27" s="19">
         <v>0.48846277999999999</v>
       </c>
       <c r="J27" s="5">
@@ -2048,7 +2066,8 @@
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I28" s="5" t="s">
+      <c r="B28" s="23"/>
+      <c r="I28" s="19" t="s">
         <v>46</v>
       </c>
       <c r="J28" s="5" t="s">
@@ -2063,7 +2082,10 @@
       <c r="A29" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="I29" s="5">
+      <c r="B29" s="23">
+        <v>5.8846080000000002E-2</v>
+      </c>
+      <c r="I29" s="19">
         <v>5.0462090000000001E-2</v>
       </c>
       <c r="J29" s="5">

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IndexY\Desktop\paralle_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592D2456-DD10-4BFE-83DC-4A67D56F5B95}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE32D3D0-0968-4026-9037-F07A3BE21B22}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -306,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -359,6 +359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -664,7 +665,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="5" customWidth="1"/>
@@ -985,7 +986,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="16">
-        <v>-2.57</v>
+        <v>0</v>
       </c>
       <c r="C6" s="16">
         <v>0</v>
@@ -2099,6 +2100,50 @@
       </c>
       <c r="M29" s="19">
         <v>5.9116960000000003E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I32" s="24">
+        <f>I19+90</f>
+        <v>75</v>
+      </c>
+      <c r="J32" s="24">
+        <f>J19+90</f>
+        <v>80</v>
+      </c>
+      <c r="K32" s="24">
+        <f t="shared" ref="K32:M32" si="0">K19+90</f>
+        <v>80</v>
+      </c>
+      <c r="L32" s="24">
+        <f t="shared" si="0"/>
+        <v>69.7</v>
+      </c>
+      <c r="M32" s="24">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I33" s="24">
+        <f>I21-90</f>
+        <v>45</v>
+      </c>
+      <c r="J33" s="24">
+        <f t="shared" ref="J33:M33" si="1">J21-90</f>
+        <v>43.599999999999994</v>
+      </c>
+      <c r="K33" s="24">
+        <f t="shared" si="1"/>
+        <v>46.900000000000006</v>
+      </c>
+      <c r="L33" s="24">
+        <f t="shared" si="1"/>
+        <v>42.66</v>
+      </c>
+      <c r="M33" s="24">
+        <f t="shared" si="1"/>
+        <v>43.400000000000006</v>
       </c>
     </row>
   </sheetData>
